--- a/03_Outputs/all/03_DS/ds_idx3_climatico.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx3_climatico.xlsx
@@ -393,13 +393,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.6882327154245143</v>
+        <v>0.6882327154245147</v>
       </c>
       <c r="D2">
-        <v>0.2284865585216002</v>
+        <v>0.2284865585216015</v>
       </c>
       <c r="E2">
-        <v>0.2014818934561676</v>
+        <v>0.2014818934561672</v>
       </c>
     </row>
     <row r="3">
@@ -414,13 +414,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.5751777650141761</v>
+        <v>-0.5751777650141749</v>
       </c>
       <c r="D3">
-        <v>0.04011374946602968</v>
+        <v>0.04011374946602736</v>
       </c>
       <c r="E3">
-        <v>0.5749460114502868</v>
+        <v>0.5749460114502867</v>
       </c>
     </row>
     <row r="4">
@@ -435,13 +435,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.3833645662832617</v>
+        <v>-0.3833645662832605</v>
       </c>
       <c r="D4">
-        <v>0.2912276272556937</v>
+        <v>0.2912276272556896</v>
       </c>
       <c r="E4">
-        <v>0.9829876198297062</v>
+        <v>0.9829876198297068</v>
       </c>
     </row>
     <row r="5">
@@ -456,13 +456,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.2078864447264168</v>
+        <v>-0.207886444726416</v>
       </c>
       <c r="D5">
-        <v>0.5020727555316098</v>
+        <v>0.5020727555316062</v>
       </c>
       <c r="E5">
-        <v>0.9316230990001945</v>
+        <v>0.9316230990001959</v>
       </c>
     </row>
     <row r="6">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.4829921705947777</v>
+        <v>-0.4829921705947778</v>
       </c>
       <c r="D6">
-        <v>0.4771327803128474</v>
+        <v>0.477132780312849</v>
       </c>
       <c r="E6">
-        <v>-0.1720088412210383</v>
+        <v>-0.1720088412210364</v>
       </c>
     </row>
     <row r="7">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.09216454963437538</v>
+        <v>0.09216454963437759</v>
       </c>
       <c r="D7">
-        <v>-0.8821573552256529</v>
+        <v>-0.8821573552256557</v>
       </c>
       <c r="E7">
-        <v>0.843984374938097</v>
+        <v>0.843984374938092</v>
       </c>
     </row>
     <row r="8">
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.01853984184951015</v>
+        <v>0.01853984184951177</v>
       </c>
       <c r="D8">
-        <v>-0.2512205124534827</v>
+        <v>-0.2512205124534853</v>
       </c>
       <c r="E8">
-        <v>0.7935118662618358</v>
+        <v>0.7935118662618337</v>
       </c>
     </row>
     <row r="9">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.03217303390557639</v>
+        <v>-0.03217303390557602</v>
       </c>
       <c r="D9">
-        <v>0.654626204528923</v>
+        <v>0.6546262045289207</v>
       </c>
       <c r="E9">
-        <v>0.7212396620457328</v>
+        <v>0.7212396620457346</v>
       </c>
     </row>
     <row r="10">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.5325395434240778</v>
+        <v>0.5325395434240814</v>
       </c>
       <c r="D10">
-        <v>-2.072299808179249</v>
+        <v>-2.072299808179251</v>
       </c>
       <c r="E10">
-        <v>0.6922759035648094</v>
+        <v>0.6922759035647986</v>
       </c>
     </row>
     <row r="11">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C11">
-        <v>-1.557007924648076</v>
+        <v>-1.557007924648074</v>
       </c>
       <c r="D11">
-        <v>-1.400948966554999</v>
+        <v>-1.400948966554998</v>
       </c>
       <c r="E11">
-        <v>-0.4664846889803272</v>
+        <v>-0.4664846889803327</v>
       </c>
     </row>
     <row r="12">
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.08364258198989337</v>
+        <v>0.08364258198989361</v>
       </c>
       <c r="D12">
-        <v>0.7382687769184958</v>
+        <v>0.738268776918494</v>
       </c>
       <c r="E12">
-        <v>0.6420844802463855</v>
+        <v>0.6420844802463878</v>
       </c>
     </row>
     <row r="13">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>-3.305970820124539</v>
+        <v>-3.30597082012454</v>
       </c>
       <c r="D13">
-        <v>-0.5165646468729292</v>
+        <v>-0.5165646468729164</v>
       </c>
       <c r="E13">
-        <v>-3.168454574123017</v>
+        <v>-3.168454574123016</v>
       </c>
     </row>
     <row r="14">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.3936575327923956</v>
+        <v>-0.3936575327923938</v>
       </c>
       <c r="D14">
-        <v>-0.7364401130311679</v>
+        <v>-0.7364401130311701</v>
       </c>
       <c r="E14">
-        <v>0.560637153165177</v>
+        <v>0.5606371531651733</v>
       </c>
     </row>
     <row r="15">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.6427186426922962</v>
+        <v>-0.642718642692292</v>
       </c>
       <c r="D15">
-        <v>-1.80049108303758</v>
+        <v>-1.800491083037587</v>
       </c>
       <c r="E15">
-        <v>1.646079627092389</v>
+        <v>1.646079627092379</v>
       </c>
     </row>
     <row r="16">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.1968894165262099</v>
+        <v>-0.1968894165262088</v>
       </c>
       <c r="D16">
-        <v>0.09423229904653964</v>
+        <v>0.09423229904653685</v>
       </c>
       <c r="E16">
-        <v>0.7787761617280059</v>
+        <v>0.7787761617280053</v>
       </c>
     </row>
     <row r="17">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.3760592506312038</v>
+        <v>0.3760592506312031</v>
       </c>
       <c r="D17">
         <v>1.24143135019018</v>
       </c>
       <c r="E17">
-        <v>0.3159577173406727</v>
+        <v>0.3159577173406769</v>
       </c>
     </row>
     <row r="18">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.08997826396869195</v>
+        <v>0.08997826396869196</v>
       </c>
       <c r="D18">
-        <v>0.7903701263731062</v>
+        <v>0.7903701263731056</v>
       </c>
       <c r="E18">
-        <v>0.4231626050524041</v>
+        <v>0.4231626050524067</v>
       </c>
     </row>
     <row r="19">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.6533973916477605</v>
+        <v>-0.6533973916477591</v>
       </c>
       <c r="D19">
-        <v>0.3524163448671135</v>
+        <v>0.3524163448671074</v>
       </c>
       <c r="E19">
-        <v>1.32342773310501</v>
+        <v>1.323427733105011</v>
       </c>
     </row>
     <row r="20">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.1638580838684471</v>
+        <v>-0.1638580838684452</v>
       </c>
       <c r="D20">
-        <v>-0.4017116104387649</v>
+        <v>-0.4017116104387687</v>
       </c>
       <c r="E20">
-        <v>0.9874530265336883</v>
+        <v>0.9874530265336857</v>
       </c>
     </row>
     <row r="21">
@@ -792,13 +792,13 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.1981543312631044</v>
+        <v>-0.1981543312631022</v>
       </c>
       <c r="D21">
-        <v>-1.520933033989096</v>
+        <v>-1.520933033989095</v>
       </c>
       <c r="E21">
-        <v>-0.1750219620078304</v>
+        <v>-0.1750219620078377</v>
       </c>
     </row>
     <row r="22">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="C22">
-        <v>-1.707506702748643</v>
+        <v>-1.707506702748641</v>
       </c>
       <c r="D22">
-        <v>-1.282370947888265</v>
+        <v>-1.28237094788826</v>
       </c>
       <c r="E22">
-        <v>-1.029470077902063</v>
+        <v>-1.029470077902067</v>
       </c>
     </row>
     <row r="23">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.4138383095171639</v>
+        <v>0.4138383095171661</v>
       </c>
       <c r="D23">
-        <v>-1.106931988738841</v>
+        <v>-1.106931988738842</v>
       </c>
       <c r="E23">
-        <v>0.6199170041227813</v>
+        <v>0.6199170041227751</v>
       </c>
     </row>
     <row r="24">
@@ -858,10 +858,10 @@
         <v>-1.013516301810168</v>
       </c>
       <c r="D24">
-        <v>0.2104664911429917</v>
+        <v>0.210466491142991</v>
       </c>
       <c r="E24">
-        <v>0.1233117184711714</v>
+        <v>0.1233117184711725</v>
       </c>
     </row>
     <row r="25">
@@ -879,10 +879,10 @@
         <v>-3.614566710590284</v>
       </c>
       <c r="D25">
-        <v>-0.4998214515099025</v>
+        <v>-0.4998214515098975</v>
       </c>
       <c r="E25">
-        <v>-1.691692999244838</v>
+        <v>-1.691692999244837</v>
       </c>
     </row>
     <row r="26">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C26">
-        <v>-1.008195973876937</v>
+        <v>-1.008195973876934</v>
       </c>
       <c r="D26">
-        <v>-2.045051901551687</v>
+        <v>-2.045051901551689</v>
       </c>
       <c r="E26">
-        <v>0.3512074821199122</v>
+        <v>0.3512074821199032</v>
       </c>
     </row>
     <row r="27">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.5086603188129668</v>
+        <v>-0.5086603188129661</v>
       </c>
       <c r="D27">
-        <v>0.1010924287633305</v>
+        <v>0.1010924287633297</v>
       </c>
       <c r="E27">
-        <v>0.2956384498536681</v>
+        <v>0.2956384498536682</v>
       </c>
     </row>
     <row r="28">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.6489415118162847</v>
+        <v>0.6489415118162865</v>
       </c>
       <c r="D28">
-        <v>-0.8799295307280225</v>
+        <v>-0.8799295307280223</v>
       </c>
       <c r="E28">
-        <v>0.3977511380476485</v>
+        <v>0.397751138047643</v>
       </c>
     </row>
     <row r="29">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.7117064352094663</v>
+        <v>-0.7117064352094645</v>
       </c>
       <c r="D29">
-        <v>-0.6179916451880783</v>
+        <v>-0.6179916451880806</v>
       </c>
       <c r="E29">
-        <v>0.5344650877039342</v>
+        <v>0.5344650877039313</v>
       </c>
     </row>
     <row r="30">
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="C30">
-        <v>-1.555736507921105</v>
+        <v>-1.555736507921103</v>
       </c>
       <c r="D30">
-        <v>-0.3134463965102735</v>
+        <v>-0.3134463965102741</v>
       </c>
       <c r="E30">
-        <v>0.006342141083126569</v>
+        <v>0.006342141083125974</v>
       </c>
     </row>
     <row r="31">
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="C31">
-        <v>1.043214354674977</v>
+        <v>1.043214354674979</v>
       </c>
       <c r="D31">
-        <v>-1.023746273266104</v>
+        <v>-1.023746273266102</v>
       </c>
       <c r="E31">
-        <v>0.07605748701731453</v>
+        <v>0.07605748701730819</v>
       </c>
     </row>
     <row r="32">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.2333370182814452</v>
+        <v>0.2333370182814429</v>
       </c>
       <c r="D32">
-        <v>1.315690006776367</v>
+        <v>1.315690006776376</v>
       </c>
       <c r="E32">
-        <v>-1.421612123517749</v>
+        <v>-1.421612123517743</v>
       </c>
     </row>
     <row r="33">
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="C33">
-        <v>-0.1645768145636576</v>
+        <v>-0.1645768145636567</v>
       </c>
       <c r="D33">
-        <v>-0.3348498640465594</v>
+        <v>-0.3348498640465576</v>
       </c>
       <c r="E33">
-        <v>-0.1379320679823478</v>
+        <v>-0.1379320679823499</v>
       </c>
     </row>
     <row r="34">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.6920283411611646</v>
+        <v>-0.692028341161163</v>
       </c>
       <c r="D34">
-        <v>0.2925170575770724</v>
+        <v>0.2925170575770664</v>
       </c>
       <c r="E34">
-        <v>1.330274988545518</v>
+        <v>1.330274988545519</v>
       </c>
     </row>
     <row r="35">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.485580815670566</v>
+        <v>-0.4855808156705642</v>
       </c>
       <c r="D35">
-        <v>-0.027235188302716</v>
+        <v>-0.02723518830272165</v>
       </c>
       <c r="E35">
-        <v>1.261642895477779</v>
+        <v>1.261642895477778</v>
       </c>
     </row>
     <row r="36">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.436118077064438</v>
+        <v>0.4361180770644408</v>
       </c>
       <c r="D36">
-        <v>-1.531407804382559</v>
+        <v>-1.53140780438256</v>
       </c>
       <c r="E36">
-        <v>0.4399246613883595</v>
+        <v>0.4399246613883512</v>
       </c>
     </row>
     <row r="37">
@@ -1131,10 +1131,10 @@
         <v>0.243317658792939</v>
       </c>
       <c r="D37">
-        <v>0.4734996257445944</v>
+        <v>0.4734996257445961</v>
       </c>
       <c r="E37">
-        <v>-0.0101692080157227</v>
+        <v>-0.01016920801572162</v>
       </c>
     </row>
     <row r="38">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.6122050691407717</v>
+        <v>0.6122050691407706</v>
       </c>
       <c r="D38">
-        <v>1.36156687231173</v>
+        <v>1.361566872311732</v>
       </c>
       <c r="E38">
-        <v>0.06590190476292472</v>
+        <v>0.0659019047629294</v>
       </c>
     </row>
     <row r="39">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.2383828856521747</v>
+        <v>0.2383828856521746</v>
       </c>
       <c r="D39">
-        <v>0.802442142695608</v>
+        <v>0.8024421426956081</v>
       </c>
       <c r="E39">
-        <v>0.3184065323745972</v>
+        <v>0.3184065323745997</v>
       </c>
     </row>
     <row r="40">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="C40">
-        <v>-1.065118644713991</v>
+        <v>-1.065118644713989</v>
       </c>
       <c r="D40">
-        <v>0.01974891980561272</v>
+        <v>0.01974891980560767</v>
       </c>
       <c r="E40">
-        <v>0.998840806991267</v>
+        <v>0.9988408069912669</v>
       </c>
     </row>
     <row r="41">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.7245929360213251</v>
+        <v>0.7245929360213264</v>
       </c>
       <c r="D41">
-        <v>-0.8858055552763363</v>
+        <v>-0.8858055552763323</v>
       </c>
       <c r="E41">
-        <v>-0.363343660748531</v>
+        <v>-0.3633436607485363</v>
       </c>
     </row>
     <row r="42">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.4700906005904529</v>
+        <v>0.4700906005904526</v>
       </c>
       <c r="D42">
-        <v>0.7703619761755053</v>
+        <v>0.7703619761755069</v>
       </c>
       <c r="E42">
-        <v>0.06263398881797617</v>
+        <v>0.06263398881797846</v>
       </c>
     </row>
     <row r="43">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="C43">
-        <v>-1.430125709436209</v>
+        <v>-1.430125709436208</v>
       </c>
       <c r="D43">
-        <v>0.1280719356118299</v>
+        <v>0.1280719356118302</v>
       </c>
       <c r="E43">
-        <v>-0.1576720390097094</v>
+        <v>-0.1576720390097083</v>
       </c>
     </row>
     <row r="44">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.01970577306592659</v>
+        <v>0.01970577306592758</v>
       </c>
       <c r="D44">
-        <v>0.2222003837191823</v>
+        <v>0.2222003837191799</v>
       </c>
       <c r="E44">
         <v>0.7459710480001095</v>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="C45">
-        <v>-0.3109074968745685</v>
+        <v>-0.3109074968745671</v>
       </c>
       <c r="D45">
-        <v>0.1863703723674926</v>
+        <v>0.1863703723674882</v>
       </c>
       <c r="E45">
         <v>1.066509307096678</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C46">
-        <v>0.1109671912049598</v>
+        <v>0.1109671912049625</v>
       </c>
       <c r="D46">
         <v>-1.633095119921652</v>
       </c>
       <c r="E46">
-        <v>0.1799554308082838</v>
+        <v>0.1799554308082756</v>
       </c>
     </row>
     <row r="47">
@@ -1338,13 +1338,13 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.06821102623654647</v>
+        <v>-0.06821102623654504</v>
       </c>
       <c r="D47">
-        <v>0.02805511789648266</v>
+        <v>0.02805511789647946</v>
       </c>
       <c r="E47">
-        <v>0.8958948389032522</v>
+        <v>0.8958948389032514</v>
       </c>
     </row>
     <row r="48">
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.9675892512252068</v>
+        <v>0.9675892512252066</v>
       </c>
       <c r="D48">
-        <v>0.5157643666689119</v>
+        <v>0.5157643666689149</v>
       </c>
       <c r="E48">
-        <v>-0.06436746432974114</v>
+        <v>-0.06436746432974051</v>
       </c>
     </row>
     <row r="49">
@@ -1383,10 +1383,10 @@
         <v>-0.2911656789924191</v>
       </c>
       <c r="D49">
-        <v>0.4664031741812786</v>
+        <v>0.4664031741812803</v>
       </c>
       <c r="E49">
-        <v>-0.1448249910592401</v>
+        <v>-0.1448249910592385</v>
       </c>
     </row>
     <row r="50">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.1298975399394581</v>
+        <v>-0.1298975399394577</v>
       </c>
       <c r="D50">
-        <v>0.6814004128581653</v>
+        <v>0.681400412858163</v>
       </c>
       <c r="E50">
-        <v>0.7150111022125287</v>
+        <v>0.7150111022125308</v>
       </c>
     </row>
     <row r="51">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.631908882646364</v>
+        <v>-0.6319088826463621</v>
       </c>
       <c r="D51">
-        <v>0.1852172448238773</v>
+        <v>0.1852172448238711</v>
       </c>
       <c r="E51">
         <v>1.355123203611421</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.4928233825059365</v>
+        <v>-0.492823382505936</v>
       </c>
       <c r="D52">
-        <v>0.411880147611791</v>
+        <v>0.41188014761179</v>
       </c>
       <c r="E52">
-        <v>0.3464938190427337</v>
+        <v>0.346493819042735</v>
       </c>
     </row>
     <row r="53">
@@ -1464,13 +1464,13 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.5320003025717237</v>
+        <v>0.5320003025717244</v>
       </c>
       <c r="D53">
-        <v>0.0732588788921938</v>
+        <v>0.07325887889219404</v>
       </c>
       <c r="E53">
-        <v>0.3608176754532707</v>
+        <v>0.3608176754532696</v>
       </c>
     </row>
     <row r="54">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.5962396191293411</v>
+        <v>-0.5962396191293395</v>
       </c>
       <c r="D54">
-        <v>0.2607332169538877</v>
+        <v>0.2607332169538818</v>
       </c>
       <c r="E54">
-        <v>1.301699957935714</v>
+        <v>1.301699957935715</v>
       </c>
     </row>
     <row r="55">
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="C55">
-        <v>-1.968025087378809</v>
+        <v>-1.968025087378808</v>
       </c>
       <c r="D55">
-        <v>-0.9393356189660271</v>
+        <v>-0.9393356189660234</v>
       </c>
       <c r="E55">
-        <v>-1.021427714864978</v>
+        <v>-1.021427714864981</v>
       </c>
     </row>
     <row r="56">
@@ -1527,13 +1527,13 @@
         </is>
       </c>
       <c r="C56">
-        <v>-0.0294491298248321</v>
+        <v>-0.0294491298248303</v>
       </c>
       <c r="D56">
-        <v>-0.4153373674289379</v>
+        <v>-0.4153373674289413</v>
       </c>
       <c r="E56">
-        <v>0.9284829593711785</v>
+        <v>0.9284829593711756</v>
       </c>
     </row>
     <row r="57">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="C57">
-        <v>-0.0344612465824722</v>
+        <v>-0.03446124658247163</v>
       </c>
       <c r="D57">
-        <v>0.5426223189442012</v>
+        <v>0.5426223189441992</v>
       </c>
       <c r="E57">
-        <v>0.6566050786175386</v>
+        <v>0.65660507861754</v>
       </c>
     </row>
     <row r="58">
@@ -1572,10 +1572,10 @@
         <v>-1.48286096584787</v>
       </c>
       <c r="D58">
-        <v>0.1403326787476568</v>
+        <v>0.1403326787476596</v>
       </c>
       <c r="E58">
-        <v>-0.6819019467133419</v>
+        <v>-0.6819019467133405</v>
       </c>
     </row>
     <row r="59">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="C59">
-        <v>-0.3811871105743621</v>
+        <v>-0.3811871105743624</v>
       </c>
       <c r="D59">
-        <v>0.2093881029829366</v>
+        <v>0.2093881029829406</v>
       </c>
       <c r="E59">
-        <v>-0.6407918007227582</v>
+        <v>-0.6407918007227575</v>
       </c>
     </row>
     <row r="60">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.9797896278456648</v>
+        <v>0.9797896278456636</v>
       </c>
       <c r="D60">
-        <v>1.367227035263022</v>
+        <v>1.367227035263026</v>
       </c>
       <c r="E60">
-        <v>-0.2036054349922225</v>
+        <v>-0.203605434992218</v>
       </c>
     </row>
     <row r="61">
@@ -1632,13 +1632,13 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.9261275964553554</v>
+        <v>-0.926127596455355</v>
       </c>
       <c r="D61">
-        <v>0.5403359632644651</v>
+        <v>0.5403359632644643</v>
       </c>
       <c r="E61">
-        <v>0.1501303621630308</v>
+        <v>0.1501303621630331</v>
       </c>
     </row>
     <row r="62">
@@ -1653,13 +1653,13 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.173044273153223</v>
+        <v>0.1730442731532233</v>
       </c>
       <c r="D62">
-        <v>0.7128699976830704</v>
+        <v>0.7128699976830689</v>
       </c>
       <c r="E62">
-        <v>0.5860019628310253</v>
+        <v>0.5860019628310273</v>
       </c>
     </row>
     <row r="63">
@@ -1674,13 +1674,13 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.2156388729325124</v>
+        <v>0.2156388729325127</v>
       </c>
       <c r="D63">
-        <v>0.4622925133025454</v>
+        <v>0.4622925133025443</v>
       </c>
       <c r="E63">
-        <v>0.5598477579720327</v>
+        <v>0.5598477579720336</v>
       </c>
     </row>
     <row r="64">
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.2048404677446144</v>
+        <v>0.2048404677446151</v>
       </c>
       <c r="D64">
-        <v>0.3372031287822885</v>
+        <v>0.3372031287822871</v>
       </c>
       <c r="E64">
-        <v>0.6063161808389618</v>
+        <v>0.6063161808389621</v>
       </c>
     </row>
     <row r="65">
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.2397685141183206</v>
+        <v>0.2397685141183218</v>
       </c>
       <c r="D65">
-        <v>-0.1124679698275979</v>
+        <v>-0.1124679698275995</v>
       </c>
       <c r="E65">
-        <v>0.6494133905143631</v>
+        <v>0.6494133905143613</v>
       </c>
     </row>
     <row r="66">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="C66">
-        <v>1.902479266764231</v>
+        <v>1.902479266764227</v>
       </c>
       <c r="D66">
-        <v>2.74715213944273</v>
+        <v>2.747152139442741</v>
       </c>
       <c r="E66">
-        <v>-1.346776685704647</v>
+        <v>-1.346776685704637</v>
       </c>
     </row>
     <row r="67">
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="C67">
-        <v>-0.2647474996521322</v>
+        <v>-0.2647474996521316</v>
       </c>
       <c r="D67">
-        <v>0.7138249265490031</v>
+        <v>0.7138249265489992</v>
       </c>
       <c r="E67">
-        <v>0.9481507044032075</v>
+        <v>0.9481507044032098</v>
       </c>
     </row>
     <row r="68">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>-0.7699346252838456</v>
+        <v>-0.7699346252838439</v>
       </c>
       <c r="D68">
-        <v>0.2005813012423335</v>
+        <v>0.2005813012423276</v>
       </c>
       <c r="E68">
         <v>1.223431897630169</v>
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="C69">
-        <v>1.090542762417227</v>
+        <v>1.090542762417228</v>
       </c>
       <c r="D69">
-        <v>-1.141505036069347</v>
+        <v>-1.14150503606934</v>
       </c>
       <c r="E69">
-        <v>-0.8826204790760684</v>
+        <v>-0.882620479076075</v>
       </c>
     </row>
     <row r="70">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="C70">
-        <v>0.6261493373443123</v>
+        <v>0.6261493373443117</v>
       </c>
       <c r="D70">
-        <v>1.071730092343627</v>
+        <v>1.071730092343629</v>
       </c>
       <c r="E70">
-        <v>0.142835500082829</v>
+        <v>0.1428355000828323</v>
       </c>
     </row>
     <row r="71">
@@ -1845,10 +1845,10 @@
         <v>0.6043485086798422</v>
       </c>
       <c r="D71">
-        <v>-0.02503765903349797</v>
+        <v>-0.02503765903349281</v>
       </c>
       <c r="E71">
-        <v>-0.6089554305344806</v>
+        <v>-0.608955430534482</v>
       </c>
     </row>
     <row r="72">
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="C72">
-        <v>-1.556267046911289</v>
+        <v>-1.55626704691129</v>
       </c>
       <c r="D72">
-        <v>0.8099299254011029</v>
+        <v>0.8099299254011081</v>
       </c>
       <c r="E72">
-        <v>-1.195533298417024</v>
+        <v>-1.195533298417019</v>
       </c>
     </row>
     <row r="73">
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="C73">
-        <v>0.3063604226333337</v>
+        <v>0.3063604226333342</v>
       </c>
       <c r="D73">
-        <v>0.2295488087039821</v>
+        <v>0.2295488087039823</v>
       </c>
       <c r="E73">
-        <v>0.2945841959702475</v>
+        <v>0.2945841959702473</v>
       </c>
     </row>
     <row r="74">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="C74">
-        <v>-1.146262667246382</v>
+        <v>-1.146262667246381</v>
       </c>
       <c r="D74">
-        <v>0.1689444882772538</v>
+        <v>0.1689444882772494</v>
       </c>
       <c r="E74">
-        <v>0.8276526968590452</v>
+        <v>0.8276526968590459</v>
       </c>
     </row>
     <row r="75">
@@ -1929,10 +1929,10 @@
         <v>1.509578357448127</v>
       </c>
       <c r="D75">
-        <v>0.1717734343432769</v>
+        <v>0.1717734343432831</v>
       </c>
       <c r="E75">
-        <v>-0.5551081829891683</v>
+        <v>-0.5551081829891695</v>
       </c>
     </row>
     <row r="76">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="C76">
-        <v>1.600019332580125</v>
+        <v>1.600019332580126</v>
       </c>
       <c r="D76">
-        <v>-0.3977791517842869</v>
+        <v>-0.3977791517842802</v>
       </c>
       <c r="E76">
-        <v>-0.6862004435848408</v>
+        <v>-0.6862004435848447</v>
       </c>
     </row>
     <row r="77">
@@ -1971,10 +1971,10 @@
         <v>-1.851941108436428</v>
       </c>
       <c r="D77">
-        <v>0.06950749432354446</v>
+        <v>0.06950749432354597</v>
       </c>
       <c r="E77">
-        <v>-0.5108507747176776</v>
+        <v>-0.5108507747176763</v>
       </c>
     </row>
     <row r="78">
@@ -1992,10 +1992,10 @@
         <v>0.1229545834107654</v>
       </c>
       <c r="D78">
-        <v>0.8383522599625397</v>
+        <v>0.8383522599625393</v>
       </c>
       <c r="E78">
-        <v>0.3938895568598876</v>
+        <v>0.3938895568598902</v>
       </c>
     </row>
     <row r="79">
@@ -2010,13 +2010,13 @@
         </is>
       </c>
       <c r="C79">
-        <v>-0.6570312946956769</v>
+        <v>-0.6570312946956759</v>
       </c>
       <c r="D79">
-        <v>0.2877665604423139</v>
+        <v>0.2877665604423101</v>
       </c>
       <c r="E79">
-        <v>0.8148692640085287</v>
+        <v>0.8148692640085297</v>
       </c>
     </row>
     <row r="80">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.3154059287865865</v>
+        <v>0.3154059287865877</v>
       </c>
       <c r="D80">
-        <v>-0.1310852725022556</v>
+        <v>-0.1310852725022567</v>
       </c>
       <c r="E80">
-        <v>0.5527002239790917</v>
+        <v>0.5527002239790899</v>
       </c>
     </row>
     <row r="81">
@@ -2055,10 +2055,10 @@
         <v>2.909121466791885</v>
       </c>
       <c r="D81">
-        <v>-0.5994466322531444</v>
+        <v>-0.5994466322531311</v>
       </c>
       <c r="E81">
-        <v>-1.608572781805721</v>
+        <v>-1.608572781805727</v>
       </c>
     </row>
     <row r="82">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="C82">
-        <v>2.226056566942174</v>
+        <v>2.226056566942173</v>
       </c>
       <c r="D82">
-        <v>0.005998607504553068</v>
+        <v>0.005998607504563047</v>
       </c>
       <c r="E82">
-        <v>-1.191737091618714</v>
+        <v>-1.191737091618716</v>
       </c>
     </row>
     <row r="83">
@@ -2097,10 +2097,10 @@
         <v>1.842031546646269</v>
       </c>
       <c r="D83">
-        <v>-0.2113524176646535</v>
+        <v>-0.211352417664646</v>
       </c>
       <c r="E83">
-        <v>-0.7886367518937374</v>
+        <v>-0.7886367518937408</v>
       </c>
     </row>
     <row r="84">
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="C84">
-        <v>1.826827938241819</v>
+        <v>1.826827938241822</v>
       </c>
       <c r="D84">
-        <v>-3.184739212500963</v>
+        <v>-3.184739212500956</v>
       </c>
       <c r="E84">
-        <v>-0.5219688701030657</v>
+        <v>-0.5219688701030822</v>
       </c>
     </row>
     <row r="85">
@@ -2139,10 +2139,10 @@
         <v>1.869490340028403</v>
       </c>
       <c r="D85">
-        <v>-0.568045327554336</v>
+        <v>-0.5680453275543265</v>
       </c>
       <c r="E85">
-        <v>-1.141297781419786</v>
+        <v>-1.141297781419791</v>
       </c>
     </row>
     <row r="86">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="C86">
-        <v>2.280777365275677</v>
+        <v>2.280777365275675</v>
       </c>
       <c r="D86">
-        <v>1.443224020521353</v>
+        <v>1.443224020521364</v>
       </c>
       <c r="E86">
-        <v>-1.34095121943559</v>
+        <v>-1.340951219435586</v>
       </c>
     </row>
     <row r="87">
@@ -2181,10 +2181,10 @@
         <v>-0.3859399493636065</v>
       </c>
       <c r="D87">
-        <v>0.8554647023410124</v>
+        <v>0.8554647023410119</v>
       </c>
       <c r="E87">
-        <v>0.2363844829893526</v>
+        <v>0.2363844829893559</v>
       </c>
     </row>
     <row r="88">
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="C88">
-        <v>1.932745126678979</v>
+        <v>1.932745126678976</v>
       </c>
       <c r="D88">
-        <v>2.023279098906757</v>
+        <v>2.023279098906767</v>
       </c>
       <c r="E88">
-        <v>-1.118852217114365</v>
+        <v>-1.118852217114358</v>
       </c>
     </row>
     <row r="89">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.7812714295143145</v>
+        <v>0.7812714295143156</v>
       </c>
       <c r="D89">
-        <v>-0.392430334159091</v>
+        <v>-0.3924303341590896</v>
       </c>
       <c r="E89">
-        <v>0.2118996574453327</v>
+        <v>0.2118996574453294</v>
       </c>
     </row>
     <row r="90">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="C90">
-        <v>-0.5853852761635903</v>
+        <v>-0.5853852761635905</v>
       </c>
       <c r="D90">
-        <v>0.2941209009004481</v>
+        <v>0.2941209009004515</v>
       </c>
       <c r="E90">
-        <v>-0.5707892752248878</v>
+        <v>-0.5707892752248864</v>
       </c>
     </row>
     <row r="91">
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.7145834314415418</v>
+        <v>0.7145834314415417</v>
       </c>
       <c r="D91">
-        <v>0.357180592901726</v>
+        <v>0.3571805929017288</v>
       </c>
       <c r="E91">
-        <v>-0.09933949552503693</v>
+        <v>-0.09933949552503682</v>
       </c>
     </row>
     <row r="92">
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="C92">
-        <v>-1.486259920178444</v>
+        <v>-1.486259920178443</v>
       </c>
       <c r="D92">
-        <v>-0.7103182226927275</v>
+        <v>-0.7103182226927217</v>
       </c>
       <c r="E92">
-        <v>-1.295872510020205</v>
+        <v>-1.295872510020207</v>
       </c>
     </row>
     <row r="93">
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.9232028705829065</v>
+        <v>0.9232028705829054</v>
       </c>
       <c r="D93">
-        <v>1.437907876149578</v>
+        <v>1.437907876149582</v>
       </c>
       <c r="E93">
-        <v>-0.2148698207129848</v>
+        <v>-0.21486982071298</v>
       </c>
     </row>
     <row r="94">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="C94">
-        <v>-0.7201414755587563</v>
+        <v>-0.7201414755587547</v>
       </c>
       <c r="D94">
-        <v>0.3493006771245467</v>
+        <v>0.3493006771245406</v>
       </c>
       <c r="E94">
-        <v>1.267634392791768</v>
+        <v>1.267634392791769</v>
       </c>
     </row>
     <row r="95">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="C95">
-        <v>1.251922312250423</v>
+        <v>1.251922312250421</v>
       </c>
       <c r="D95">
-        <v>0.8311859194682915</v>
+        <v>0.831185919468299</v>
       </c>
       <c r="E95">
-        <v>-0.937592929524941</v>
+        <v>-0.9375929295249389</v>
       </c>
     </row>
     <row r="96">
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="C96">
-        <v>0.0822504504695806</v>
+        <v>0.08225045046958307</v>
       </c>
       <c r="D96">
-        <v>-1.160882478004357</v>
+        <v>-1.160882478004359</v>
       </c>
       <c r="E96">
-        <v>0.6721074449426314</v>
+        <v>0.6721074449426252</v>
       </c>
     </row>
     <row r="97">
@@ -2388,13 +2388,13 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.9601764800699126</v>
+        <v>0.9601764800699116</v>
       </c>
       <c r="D97">
-        <v>1.187302856800623</v>
+        <v>1.187302856800627</v>
       </c>
       <c r="E97">
-        <v>-0.1600914797713242</v>
+        <v>-0.1600914797713204</v>
       </c>
     </row>
     <row r="98">
@@ -2409,13 +2409,13 @@
         </is>
       </c>
       <c r="C98">
-        <v>0.07324946738615085</v>
+        <v>0.07324946738615301</v>
       </c>
       <c r="D98">
-        <v>-1.389125660936425</v>
+        <v>-1.389125660936423</v>
       </c>
       <c r="E98">
-        <v>-0.08343442809009265</v>
+        <v>-0.08343442809009971</v>
       </c>
     </row>
     <row r="99">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="C99">
-        <v>-0.1057977327091537</v>
+        <v>-0.1057977327091524</v>
       </c>
       <c r="D99">
-        <v>-0.01225747582746456</v>
+        <v>-0.01225747582746783</v>
       </c>
       <c r="E99">
-        <v>0.8971331573465458</v>
+        <v>0.8971331573465448</v>
       </c>
     </row>
     <row r="100">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.7170739906580509</v>
+        <v>0.7170739906580519</v>
       </c>
       <c r="D100">
-        <v>-0.4127129264775134</v>
+        <v>-0.4127129264775119</v>
       </c>
       <c r="E100">
-        <v>0.1611209336172672</v>
+        <v>0.1611209336172639</v>
       </c>
     </row>
     <row r="101">
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.02563220604036095</v>
+        <v>0.02563220604036159</v>
       </c>
       <c r="D101">
-        <v>0.4808973736616567</v>
+        <v>0.4808973736616544</v>
       </c>
       <c r="E101">
-        <v>0.7397216439830108</v>
+        <v>0.7397216439830119</v>
       </c>
     </row>
     <row r="102">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.324113477392952</v>
+        <v>0.3241134773929523</v>
       </c>
       <c r="D102">
-        <v>0.3410249616306641</v>
+        <v>0.3410249616306651</v>
       </c>
       <c r="E102">
-        <v>0.1607912477853102</v>
+        <v>0.1607912477853106</v>
       </c>
     </row>
     <row r="103">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="C103">
-        <v>0.8667481236937612</v>
+        <v>0.866748123693761</v>
       </c>
       <c r="D103">
-        <v>0.5849764219989138</v>
+        <v>0.5849764219989162</v>
       </c>
       <c r="E103">
-        <v>-0.008998543557449267</v>
+        <v>-0.008998543557448299</v>
       </c>
     </row>
     <row r="104">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="C104">
-        <v>-0.1240697587657531</v>
+        <v>-0.1240697587657521</v>
       </c>
       <c r="D104">
-        <v>0.371669462341682</v>
+        <v>0.3716694623416788</v>
       </c>
       <c r="E104">
-        <v>0.8768610793206115</v>
+        <v>0.8768610793206123</v>
       </c>
     </row>
     <row r="105">
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="C105">
-        <v>-0.04782012419773966</v>
+        <v>-0.04782012419774073</v>
       </c>
       <c r="D105">
-        <v>1.242742702242399</v>
+        <v>1.242742702242402</v>
       </c>
       <c r="E105">
-        <v>-0.3356798636215758</v>
+        <v>-0.3356798636215708</v>
       </c>
     </row>
     <row r="106">
@@ -2577,13 +2577,13 @@
         </is>
       </c>
       <c r="C106">
-        <v>2.412762499065351</v>
+        <v>2.412762499065352</v>
       </c>
       <c r="D106">
-        <v>-2.000940177828434</v>
+        <v>-2.000940177828425</v>
       </c>
       <c r="E106">
-        <v>-0.9262825737648853</v>
+        <v>-0.926282573764897</v>
       </c>
     </row>
     <row r="107">
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="C107">
-        <v>1.328853603302243</v>
+        <v>1.328853603302242</v>
       </c>
       <c r="D107">
-        <v>1.140902731511454</v>
+        <v>1.140902731511459</v>
       </c>
       <c r="E107">
-        <v>-0.4687919166631268</v>
+        <v>-0.4687919166631234</v>
       </c>
     </row>
     <row r="108">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="C108">
-        <v>-0.8332912490644456</v>
+        <v>-0.8332912490644445</v>
       </c>
       <c r="D108">
-        <v>-0.002901305257994692</v>
+        <v>-0.002901305257996978</v>
       </c>
       <c r="E108">
-        <v>0.4929370784558852</v>
+        <v>0.4929370784558851</v>
       </c>
     </row>
     <row r="109">
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.4654394797994212</v>
+        <v>-0.4654394797994227</v>
       </c>
       <c r="D109">
-        <v>1.090642974491688</v>
+        <v>1.090642974491695</v>
       </c>
       <c r="E109">
-        <v>-1.152446987496725</v>
+        <v>-1.15244698749672</v>
       </c>
     </row>
     <row r="110">
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="C110">
-        <v>0.4175616446733918</v>
+        <v>0.4175616446733932</v>
       </c>
       <c r="D110">
-        <v>-0.5329240561838927</v>
+        <v>-0.532924056183893</v>
       </c>
       <c r="E110">
-        <v>0.4428334304768656</v>
+        <v>0.4428334304768618</v>
       </c>
     </row>
     <row r="111">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="C111">
-        <v>-0.06651292588807649</v>
+        <v>-0.06651292588807733</v>
       </c>
       <c r="D111">
-        <v>0.8499280224945234</v>
+        <v>0.8499280224945271</v>
       </c>
       <c r="E111">
-        <v>-0.5322061051277257</v>
+        <v>-0.5322061051277225</v>
       </c>
     </row>
     <row r="112">
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="C112">
-        <v>-0.06894791949738971</v>
+        <v>-0.06894791949738938</v>
       </c>
       <c r="D112">
-        <v>0.837225593005784</v>
+        <v>0.8372255930057813</v>
       </c>
       <c r="E112">
-        <v>0.7584684730460935</v>
+        <v>0.7584684730460963</v>
       </c>
     </row>
     <row r="113">
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="C113">
-        <v>-1.860257299792151</v>
+        <v>-1.860257299792155</v>
       </c>
       <c r="D113">
-        <v>1.33323902863192</v>
+        <v>1.333239028631937</v>
       </c>
       <c r="E113">
-        <v>-3.586370841330957</v>
+        <v>-3.586370841330948</v>
       </c>
     </row>
     <row r="114">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.3299143514734041</v>
+        <v>-0.3299143514734024</v>
       </c>
       <c r="D114">
-        <v>-0.4505335601596676</v>
+        <v>-0.4505335601596701</v>
       </c>
       <c r="E114">
-        <v>0.6662720169299325</v>
+        <v>0.6662720169299297</v>
       </c>
     </row>
     <row r="115">
@@ -2769,10 +2769,10 @@
         <v>-1.031907461118801</v>
       </c>
       <c r="D115">
-        <v>0.210098191956943</v>
+        <v>0.2100981919569499</v>
       </c>
       <c r="E115">
-        <v>-1.391617152173108</v>
+        <v>-1.391617152173107</v>
       </c>
     </row>
     <row r="116">
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="C116">
-        <v>-0.6282132988445126</v>
+        <v>-0.6282132988445113</v>
       </c>
       <c r="D116">
-        <v>0.1854595922259014</v>
+        <v>0.185459592225896</v>
       </c>
       <c r="E116">
         <v>1.135391815325343</v>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C117">
-        <v>0.4405355455694107</v>
+        <v>0.4405355455694118</v>
       </c>
       <c r="D117">
-        <v>-0.1700311484788627</v>
+        <v>-0.1700311484788629</v>
       </c>
       <c r="E117">
-        <v>0.4111432088610503</v>
+        <v>0.4111432088610481</v>
       </c>
     </row>
     <row r="118">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="C118">
-        <v>-1.019750788422719</v>
+        <v>-1.019750788422722</v>
       </c>
       <c r="D118">
-        <v>1.182390681621717</v>
+        <v>1.182390681621728</v>
       </c>
       <c r="E118">
-        <v>-2.123975342400827</v>
+        <v>-2.12397534240082</v>
       </c>
     </row>
     <row r="119">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="C119">
-        <v>1.032826965307373</v>
+        <v>1.032826965307376</v>
       </c>
       <c r="D119">
-        <v>-2.651072763992925</v>
+        <v>-2.651072763992922</v>
       </c>
       <c r="E119">
-        <v>-0.09472787512650759</v>
+        <v>-0.09472787512652125</v>
       </c>
     </row>
     <row r="120">
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.1717885175402321</v>
+        <v>0.1717885175402316</v>
       </c>
       <c r="D120">
-        <v>1.189053934298726</v>
+        <v>1.189053934298725</v>
       </c>
       <c r="E120">
-        <v>0.3920410600838085</v>
+        <v>0.3920410600838126</v>
       </c>
     </row>
     <row r="121">
@@ -2892,13 +2892,13 @@
         </is>
       </c>
       <c r="C121">
-        <v>-2.475543510870484</v>
+        <v>-2.475543510870485</v>
       </c>
       <c r="D121">
-        <v>0.5309702655089875</v>
+        <v>0.5309702655089933</v>
       </c>
       <c r="E121">
-        <v>-1.548102611882032</v>
+        <v>-1.548102611882028</v>
       </c>
     </row>
     <row r="122">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="C122">
-        <v>0.2938881905190703</v>
+        <v>0.2938881905190724</v>
       </c>
       <c r="D122">
-        <v>-2.561910690317155</v>
+        <v>-2.561910690317148</v>
       </c>
       <c r="E122">
-        <v>-1.091110496079708</v>
+        <v>-1.09111049607972</v>
       </c>
     </row>
     <row r="123">
@@ -2934,13 +2934,13 @@
         </is>
       </c>
       <c r="C123">
-        <v>-0.2709784431696609</v>
+        <v>-0.2709784431696601</v>
       </c>
       <c r="D123">
-        <v>0.4320341007556133</v>
+        <v>0.4320341007556106</v>
       </c>
       <c r="E123">
-        <v>0.7454638794033255</v>
+        <v>0.7454638794033266</v>
       </c>
     </row>
     <row r="124">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="C124">
-        <v>1.016548422258893</v>
+        <v>1.016548422258895</v>
       </c>
       <c r="D124">
-        <v>-1.236523519740947</v>
+        <v>-1.236523519740945</v>
       </c>
       <c r="E124">
-        <v>0.1508068073422852</v>
+        <v>0.150806807342278</v>
       </c>
     </row>
     <row r="125">
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="C125">
-        <v>-0.07914193100700326</v>
+        <v>-0.07914193100700251</v>
       </c>
       <c r="D125">
-        <v>-2.038255741408436</v>
+        <v>-2.038255741408421</v>
       </c>
       <c r="E125">
-        <v>-2.65023770678241</v>
+        <v>-2.650237706782419</v>
       </c>
     </row>
     <row r="126">
@@ -2997,13 +2997,13 @@
         </is>
       </c>
       <c r="C126">
-        <v>1.736911380959272</v>
+        <v>1.736911380959271</v>
       </c>
       <c r="D126">
-        <v>-1.113321282444706</v>
+        <v>-1.113321282444693</v>
       </c>
       <c r="E126">
-        <v>-1.701963588173149</v>
+        <v>-1.701963588173156</v>
       </c>
     </row>
   </sheetData>
